--- a/reestr.xlsx
+++ b/reestr.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="62">
   <si>
     <t>Спортзал</t>
   </si>
@@ -154,9 +154,6 @@
     <t>НП.1</t>
   </si>
   <si>
-    <t>?</t>
-  </si>
-  <si>
     <t>№ пом.</t>
   </si>
   <si>
@@ -182,6 +179,39 @@
   </si>
   <si>
     <t>Монтаж</t>
+  </si>
+  <si>
+    <t>3.4-Ст</t>
+  </si>
+  <si>
+    <t>3.5-Ст</t>
+  </si>
+  <si>
+    <t>Дифрагм 2 шт</t>
+  </si>
+  <si>
+    <t>4.5-Ст</t>
+  </si>
+  <si>
+    <t>Швы</t>
+  </si>
+  <si>
+    <t>3.2(3.3)-Ст</t>
+  </si>
+  <si>
+    <t>3.6-Ст</t>
+  </si>
+  <si>
+    <t>3.1-Ст</t>
+  </si>
+  <si>
+    <t>4.6-Ст</t>
+  </si>
+  <si>
+    <t>4.1-Ст</t>
+  </si>
+  <si>
+    <t>4.3-Ст</t>
   </si>
 </sst>
 </file>
@@ -208,7 +238,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -221,8 +251,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="24">
+  <borders count="25">
     <border>
       <left/>
       <right/>
@@ -503,17 +539,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -523,11 +548,33 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -537,7 +584,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -560,24 +607,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -587,28 +616,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -652,6 +663,66 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -934,156 +1005,164 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:X10"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:Y11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.42578125" style="7" customWidth="1"/>
     <col min="2" max="2" width="9.28515625" style="7" customWidth="1"/>
-    <col min="3" max="5" width="7.28515625" style="8" customWidth="1"/>
-    <col min="6" max="6" width="11.5703125" style="8" customWidth="1"/>
-    <col min="7" max="20" width="8.85546875" style="8" customWidth="1"/>
-    <col min="21" max="23" width="8.85546875" style="7" customWidth="1"/>
-    <col min="24" max="24" width="10.85546875" style="7" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="7"/>
+    <col min="3" max="6" width="7.28515625" style="8" customWidth="1"/>
+    <col min="7" max="7" width="11.5703125" style="8" customWidth="1"/>
+    <col min="8" max="21" width="8.85546875" style="8" customWidth="1"/>
+    <col min="22" max="24" width="8.85546875" style="7" customWidth="1"/>
+    <col min="25" max="25" width="10.85546875" style="7" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="9"/>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="11"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="10" t="s">
+      <c r="D2" s="45"/>
+      <c r="E2" s="46"/>
+      <c r="F2" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="11"/>
-      <c r="J2" s="11"/>
-      <c r="K2" s="11"/>
-      <c r="L2" s="11"/>
-      <c r="M2" s="11"/>
-      <c r="N2" s="11"/>
-      <c r="O2" s="13" t="s">
+      <c r="G2" s="49"/>
+      <c r="H2" s="49"/>
+      <c r="I2" s="49"/>
+      <c r="J2" s="49"/>
+      <c r="K2" s="49"/>
+      <c r="L2" s="45"/>
+      <c r="M2" s="45"/>
+      <c r="N2" s="45"/>
+      <c r="O2" s="46"/>
+      <c r="P2" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="P2" s="14"/>
-      <c r="Q2" s="14"/>
-      <c r="R2" s="14"/>
-      <c r="S2" s="15"/>
-      <c r="T2" s="16"/>
-      <c r="U2" s="16"/>
-      <c r="V2" s="16"/>
-      <c r="W2" s="16"/>
-    </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Q2" s="38"/>
+      <c r="R2" s="38"/>
+      <c r="S2" s="38"/>
+      <c r="T2" s="39"/>
+      <c r="U2" s="10"/>
+      <c r="V2" s="10"/>
+      <c r="W2" s="10"/>
+      <c r="X2" s="10"/>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="9"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="18"/>
-      <c r="E3" s="19"/>
-      <c r="F3" s="20" t="s">
+      <c r="C3" s="11"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="21"/>
-      <c r="H3" s="21"/>
-      <c r="I3" s="21"/>
-      <c r="J3" s="22"/>
-      <c r="K3" s="20" t="s">
+      <c r="G3" s="38"/>
+      <c r="H3" s="38"/>
+      <c r="I3" s="38"/>
+      <c r="J3" s="38"/>
+      <c r="K3" s="39"/>
+      <c r="L3" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="L3" s="21"/>
-      <c r="M3" s="21"/>
-      <c r="N3" s="21"/>
-      <c r="O3" s="23" t="s">
+      <c r="M3" s="47"/>
+      <c r="N3" s="47"/>
+      <c r="O3" s="47"/>
+      <c r="P3" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="P3" s="24"/>
-      <c r="Q3" s="24"/>
-      <c r="R3" s="24"/>
-      <c r="S3" s="25"/>
-      <c r="T3" s="26" t="s">
+      <c r="Q3" s="41"/>
+      <c r="R3" s="41"/>
+      <c r="S3" s="41"/>
+      <c r="T3" s="42"/>
+      <c r="U3" s="37" t="s">
         <v>36</v>
       </c>
-      <c r="U3" s="14"/>
-      <c r="V3" s="14"/>
-      <c r="W3" s="14"/>
-      <c r="X3" s="15"/>
-    </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="V3" s="38"/>
+      <c r="W3" s="38"/>
+      <c r="X3" s="38"/>
+      <c r="Y3" s="39"/>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="C4" s="27"/>
+        <v>42</v>
+      </c>
+      <c r="C4" s="15"/>
       <c r="D4" s="2"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="3" t="s">
+      <c r="E4" s="17"/>
+      <c r="F4" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="G4" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="H4" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="I4" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="J4" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="J4" s="28" t="s">
+      <c r="K4" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="L4" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="L4" s="2" t="s">
+      <c r="M4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="2" t="s">
+      <c r="N4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="N4" s="29" t="s">
+      <c r="O4" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="O4" s="3" t="s">
+      <c r="P4" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="P4" s="2" t="s">
+      <c r="Q4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="Q4" s="2" t="s">
+      <c r="R4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="R4" s="2" t="s">
+      <c r="S4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="S4" s="28" t="s">
-        <v>51</v>
-      </c>
-      <c r="T4" s="30" t="s">
+      <c r="T4" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="U4" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="U4" s="2" t="s">
+      <c r="V4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="V4" s="2" t="s">
+      <c r="W4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="W4" s="2" t="s">
+      <c r="X4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="X4" s="31" t="s">
+      <c r="Y4" s="19" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="32">
+      <c r="B5" s="20">
         <v>1.03</v>
       </c>
       <c r="C5" s="5" t="s">
@@ -1092,30 +1171,32 @@
       <c r="D5" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="34" t="s">
+        <v>60</v>
+      </c>
+      <c r="G5" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4" t="s">
+      <c r="H5" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="I5" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="I5" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J5" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="K5" s="5"/>
-      <c r="L5" s="4"/>
+      <c r="J5" s="31" t="s">
+        <v>54</v>
+      </c>
+      <c r="K5" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="L5" s="22"/>
       <c r="M5" s="4"/>
-      <c r="N5" s="33"/>
-      <c r="O5" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="P5" s="4" t="s">
+      <c r="N5" s="4"/>
+      <c r="O5" s="21"/>
+      <c r="P5" s="5" t="s">
         <v>19</v>
       </c>
       <c r="Q5" s="4" t="s">
@@ -1124,38 +1205,51 @@
       <c r="R5" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="S5" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="T5" s="34"/>
-      <c r="U5" s="4"/>
-      <c r="V5" s="4"/>
-      <c r="W5" s="4"/>
-      <c r="X5" s="35"/>
-    </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="S5" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="T5" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="U5" s="30"/>
+      <c r="V5" s="31"/>
+      <c r="W5" s="31"/>
+      <c r="X5" s="31"/>
+      <c r="Y5" s="33" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="32">
+      <c r="B6" s="20">
         <v>1.032</v>
       </c>
-      <c r="C6" s="5"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="4"/>
+      <c r="C6" s="34"/>
+      <c r="D6" s="31"/>
+      <c r="E6" s="35"/>
+      <c r="F6" s="31" t="s">
+        <v>58</v>
+      </c>
+      <c r="G6" s="31" t="s">
+        <v>56</v>
+      </c>
       <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="6"/>
-      <c r="K6" s="5"/>
-      <c r="L6" s="4"/>
+      <c r="I6" s="31" t="s">
+        <v>51</v>
+      </c>
+      <c r="J6" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="K6" s="33" t="s">
+        <v>57</v>
+      </c>
+      <c r="L6" s="22"/>
       <c r="M6" s="4"/>
-      <c r="N6" s="33"/>
-      <c r="O6" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="P6" s="4" t="s">
+      <c r="N6" s="4"/>
+      <c r="O6" s="21"/>
+      <c r="P6" s="5" t="s">
         <v>19</v>
       </c>
       <c r="Q6" s="4" t="s">
@@ -1164,255 +1258,267 @@
       <c r="R6" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="S6" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="T6" s="34"/>
-      <c r="U6" s="4"/>
+      <c r="S6" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="T6" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="U6" s="22"/>
       <c r="V6" s="4"/>
       <c r="W6" s="4"/>
-      <c r="X6" s="35"/>
-    </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="X6" s="4"/>
+      <c r="Y6" s="23"/>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="32">
+      <c r="B7" s="20">
         <v>2.0219999999999998</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="2"/>
-      <c r="E7" s="28"/>
-      <c r="F7" s="3" t="s">
+      <c r="E7" s="17"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="H7" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="I7" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="I7" s="2" t="s">
+      <c r="J7" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="J7" s="2" t="s">
+      <c r="K7" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="K7" s="3" t="s">
+      <c r="L7" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="L7" s="2" t="s">
+      <c r="M7" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="M7" s="2" t="s">
+      <c r="N7" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="N7" s="29" t="s">
+      <c r="O7" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="O7" s="3" t="s">
+      <c r="P7" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="P7" s="2" t="s">
+      <c r="Q7" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="Q7" s="2" t="s">
+      <c r="R7" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="R7" s="2" t="s">
+      <c r="S7" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="S7" s="28"/>
-      <c r="T7" s="30" t="s">
+      <c r="T7" s="16"/>
+      <c r="U7" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="U7" s="2" t="s">
+      <c r="V7" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="V7" s="2" t="s">
+      <c r="W7" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="W7" s="2" t="s">
+      <c r="X7" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="X7" s="28" t="s">
+      <c r="Y7" s="16" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="32">
+      <c r="B8" s="20">
         <v>3.0190000000000001</v>
       </c>
       <c r="C8" s="3"/>
       <c r="D8" s="2"/>
-      <c r="E8" s="28"/>
-      <c r="F8" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G8" s="2" t="s">
+      <c r="E8" s="17"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="H8" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="I8" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="I8" s="2" t="s">
+      <c r="J8" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="J8" s="2" t="s">
+      <c r="K8" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="K8" s="3" t="s">
+      <c r="L8" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="L8" s="2" t="s">
+      <c r="M8" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="M8" s="2" t="s">
+      <c r="N8" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="N8" s="29" t="s">
+      <c r="O8" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="O8" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="P8" s="2" t="s">
+      <c r="P8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q8" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="Q8" s="2" t="s">
+      <c r="R8" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="R8" s="2" t="s">
+      <c r="S8" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="S8" s="28"/>
-      <c r="T8" s="30" t="s">
+      <c r="T8" s="16"/>
+      <c r="U8" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="U8" s="2" t="s">
+      <c r="V8" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="V8" s="2" t="s">
+      <c r="W8" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="W8" s="2" t="s">
+      <c r="X8" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="X8" s="28" t="s">
+      <c r="Y8" s="16" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B9" s="32">
+      <c r="B9" s="20">
         <v>2.0329999999999999</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="4"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="5" t="s">
-        <v>19</v>
-      </c>
+      <c r="E9" s="21"/>
+      <c r="F9" s="5"/>
       <c r="G9" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H9" s="4" t="s">
         <v>12</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>13</v>
       </c>
       <c r="I9" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="J9" s="6" t="s">
+      <c r="J9" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="K9" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="L9" s="4" t="s">
+      <c r="K9" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="L9" s="22" t="s">
         <v>19</v>
       </c>
       <c r="M9" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="N9" s="33" t="s">
-        <v>19</v>
-      </c>
-      <c r="O9" s="5"/>
-      <c r="P9" s="4"/>
+      <c r="N9" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="O9" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="P9" s="5"/>
       <c r="Q9" s="4"/>
       <c r="R9" s="4"/>
-      <c r="S9" s="6"/>
-      <c r="T9" s="34"/>
-      <c r="U9" s="4"/>
+      <c r="S9" s="4"/>
+      <c r="T9" s="6"/>
+      <c r="U9" s="22"/>
       <c r="V9" s="4"/>
       <c r="W9" s="4"/>
-      <c r="X9" s="35"/>
-    </row>
-    <row r="10" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="X9" s="4"/>
+      <c r="Y9" s="23"/>
+    </row>
+    <row r="10" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B10" s="32">
+      <c r="B10" s="20">
         <v>2.0369999999999999</v>
       </c>
-      <c r="C10" s="36"/>
-      <c r="D10" s="37"/>
-      <c r="E10" s="38"/>
-      <c r="F10" s="36" t="s">
+      <c r="C10" s="24"/>
+      <c r="D10" s="25"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="24"/>
+      <c r="G10" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="G10" s="37" t="s">
-        <v>19</v>
-      </c>
-      <c r="H10" s="37" t="s">
+      <c r="H10" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="I10" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="I10" s="37" t="s">
+      <c r="J10" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="J10" s="38" t="s">
+      <c r="K10" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="K10" s="36" t="s">
-        <v>19</v>
-      </c>
-      <c r="L10" s="37" t="s">
+      <c r="L10" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="M10" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="M10" s="37" t="s">
+      <c r="N10" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="N10" s="39" t="s">
+      <c r="O10" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="O10" s="36"/>
-      <c r="P10" s="37"/>
-      <c r="Q10" s="37"/>
-      <c r="R10" s="37"/>
-      <c r="S10" s="38"/>
-      <c r="T10" s="40"/>
-      <c r="U10" s="37"/>
-      <c r="V10" s="37"/>
-      <c r="W10" s="37"/>
-      <c r="X10" s="41"/>
+      <c r="P10" s="24"/>
+      <c r="Q10" s="25"/>
+      <c r="R10" s="25"/>
+      <c r="S10" s="25"/>
+      <c r="T10" s="26"/>
+      <c r="U10" s="28"/>
+      <c r="V10" s="25"/>
+      <c r="W10" s="25"/>
+      <c r="X10" s="25"/>
+      <c r="Y10" s="29"/>
+    </row>
+    <row r="11" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H11" s="25" t="s">
+        <v>19</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="T3:X3"/>
-    <mergeCell ref="O3:S3"/>
-    <mergeCell ref="O2:S2"/>
+    <mergeCell ref="U3:Y3"/>
+    <mergeCell ref="P3:T3"/>
+    <mergeCell ref="P2:T2"/>
     <mergeCell ref="C2:E2"/>
-    <mergeCell ref="F3:J3"/>
-    <mergeCell ref="F2:N2"/>
-    <mergeCell ref="K3:N3"/>
+    <mergeCell ref="L3:O3"/>
+    <mergeCell ref="F2:O2"/>
+    <mergeCell ref="F3:K3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="8" scale="82" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1429,7 +1535,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -1437,7 +1543,7 @@
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.25">
@@ -1487,7 +1593,7 @@
   <sheetData>
     <row r="2" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D2" t="s">
         <v>3</v>
@@ -1501,17 +1607,17 @@
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/reestr.xlsx
+++ b/reestr.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="63">
   <si>
     <t>Спортзал</t>
   </si>
@@ -145,9 +145,6 @@
     <t>Прим.</t>
   </si>
   <si>
-    <t>ШП.1</t>
-  </si>
-  <si>
     <t>Шт.1, Шт.2</t>
   </si>
   <si>
@@ -181,9 +178,6 @@
     <t>Монтаж</t>
   </si>
   <si>
-    <t>3.4-Ст</t>
-  </si>
-  <si>
     <t>3.5-Ст</t>
   </si>
   <si>
@@ -196,22 +190,31 @@
     <t>Швы</t>
   </si>
   <si>
-    <t>3.2(3.3)-Ст</t>
-  </si>
-  <si>
-    <t>3.6-Ст</t>
-  </si>
-  <si>
-    <t>3.1-Ст</t>
-  </si>
-  <si>
-    <t>4.6-Ст</t>
-  </si>
-  <si>
     <t>4.1-Ст</t>
   </si>
   <si>
-    <t>4.3-Ст</t>
+    <t>3.4.1-Ст</t>
+  </si>
+  <si>
+    <t>3.4.2-Ст</t>
+  </si>
+  <si>
+    <t>4.2-Ст</t>
+  </si>
+  <si>
+    <t>3.2-Ст</t>
+  </si>
+  <si>
+    <t>3.3.1-Ст</t>
+  </si>
+  <si>
+    <t>3.3.2-Ст</t>
+  </si>
+  <si>
+    <t>4.4.2-Ст</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ШП.1  </t>
   </si>
 </sst>
 </file>
@@ -548,14 +551,16 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
+      <left style="thin">
         <color indexed="64"/>
       </left>
       <right/>
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -564,14 +569,16 @@
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
       <top style="medium">
         <color indexed="64"/>
       </top>
@@ -584,7 +591,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -683,47 +690,59 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1008,157 +1027,164 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Y11"/>
+  <dimension ref="A1:Z11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.42578125" style="7" customWidth="1"/>
     <col min="2" max="2" width="9.28515625" style="7" customWidth="1"/>
-    <col min="3" max="6" width="7.28515625" style="8" customWidth="1"/>
-    <col min="7" max="7" width="11.5703125" style="8" customWidth="1"/>
-    <col min="8" max="21" width="8.85546875" style="8" customWidth="1"/>
-    <col min="22" max="24" width="8.85546875" style="7" customWidth="1"/>
-    <col min="25" max="25" width="10.85546875" style="7" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="7"/>
+    <col min="3" max="5" width="7.28515625" style="8" customWidth="1"/>
+    <col min="6" max="6" width="8.85546875" style="8" customWidth="1"/>
+    <col min="7" max="7" width="7.28515625" style="8" customWidth="1"/>
+    <col min="8" max="9" width="11.5703125" style="8" customWidth="1"/>
+    <col min="10" max="22" width="8.85546875" style="8" customWidth="1"/>
+    <col min="23" max="25" width="8.85546875" style="7" customWidth="1"/>
+    <col min="26" max="26" width="10.85546875" style="7" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="9"/>
-      <c r="C2" s="44" t="s">
+      <c r="C2" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="45"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="48" t="s">
+      <c r="D2" s="46"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="49"/>
-      <c r="H2" s="49"/>
-      <c r="I2" s="49"/>
-      <c r="J2" s="49"/>
-      <c r="K2" s="49"/>
-      <c r="L2" s="45"/>
-      <c r="M2" s="45"/>
-      <c r="N2" s="45"/>
-      <c r="O2" s="46"/>
-      <c r="P2" s="43" t="s">
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="48"/>
+      <c r="L2" s="48"/>
+      <c r="M2" s="48"/>
+      <c r="N2" s="48"/>
+      <c r="O2" s="48"/>
+      <c r="P2" s="49"/>
+      <c r="Q2" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="Q2" s="38"/>
-      <c r="R2" s="38"/>
-      <c r="S2" s="38"/>
+      <c r="R2" s="39"/>
+      <c r="S2" s="39"/>
       <c r="T2" s="39"/>
-      <c r="U2" s="10"/>
+      <c r="U2" s="40"/>
       <c r="V2" s="10"/>
       <c r="W2" s="10"/>
       <c r="X2" s="10"/>
-    </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y2" s="10"/>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="9"/>
       <c r="C3" s="11"/>
       <c r="D3" s="12"/>
       <c r="E3" s="36"/>
-      <c r="F3" s="43" t="s">
+      <c r="F3" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
-      <c r="J3" s="38"/>
-      <c r="K3" s="39"/>
-      <c r="L3" s="47" t="s">
+      <c r="G3" s="51"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="51"/>
+      <c r="K3" s="51"/>
+      <c r="L3" s="52"/>
+      <c r="M3" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="M3" s="47"/>
-      <c r="N3" s="47"/>
-      <c r="O3" s="47"/>
-      <c r="P3" s="40" t="s">
+      <c r="N3" s="50"/>
+      <c r="O3" s="50"/>
+      <c r="P3" s="50"/>
+      <c r="Q3" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="Q3" s="41"/>
-      <c r="R3" s="41"/>
-      <c r="S3" s="41"/>
+      <c r="R3" s="42"/>
+      <c r="S3" s="42"/>
       <c r="T3" s="42"/>
-      <c r="U3" s="37" t="s">
+      <c r="U3" s="43"/>
+      <c r="V3" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="V3" s="38"/>
-      <c r="W3" s="38"/>
-      <c r="X3" s="38"/>
+      <c r="W3" s="39"/>
+      <c r="X3" s="39"/>
       <c r="Y3" s="39"/>
-    </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z3" s="40"/>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C4" s="15"/>
       <c r="D4" s="2"/>
       <c r="E4" s="17"/>
-      <c r="F4" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="G4" s="14" t="s">
+      <c r="F4" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="G4" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="H4" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="H4" s="14" t="s">
+      <c r="I4" s="37" t="s">
+        <v>37</v>
+      </c>
+      <c r="J4" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="K4" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="L4" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="M4" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="I4" s="14" t="s">
+      <c r="N4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="J4" s="14" t="s">
+      <c r="O4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K4" s="16" t="s">
+      <c r="P4" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="L4" s="18" t="s">
+      <c r="Q4" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="R4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="S4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="T4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="U4" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="V4" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="M4" s="2" t="s">
+      <c r="W4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="N4" s="2" t="s">
+      <c r="X4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="O4" s="17" t="s">
+      <c r="Y4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="P4" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="R4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="S4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="T4" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="U4" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="V4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="W4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="X4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="Y4" s="19" t="s">
+      <c r="Z4" s="19" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
@@ -1166,40 +1192,40 @@
         <v>1.03</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E5" s="21" t="s">
-        <v>41</v>
-      </c>
-      <c r="F5" s="34" t="s">
-        <v>60</v>
-      </c>
-      <c r="G5" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="H5" s="31" t="s">
-        <v>61</v>
+      <c r="F5" s="31" t="s">
+        <v>54</v>
+      </c>
+      <c r="G5" s="34" t="s">
+        <v>57</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>39</v>
       </c>
       <c r="I5" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="J5" s="31" t="s">
-        <v>54</v>
-      </c>
-      <c r="K5" s="32" t="s">
-        <v>59</v>
-      </c>
-      <c r="L5" s="22"/>
-      <c r="M5" s="4"/>
+      <c r="J5" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="K5" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="L5" s="32" t="s">
+        <v>52</v>
+      </c>
+      <c r="M5" s="22"/>
       <c r="N5" s="4"/>
-      <c r="O5" s="21"/>
-      <c r="P5" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q5" s="4" t="s">
+      <c r="O5" s="4"/>
+      <c r="P5" s="21"/>
+      <c r="Q5" s="5" t="s">
         <v>19</v>
       </c>
       <c r="R5" s="4" t="s">
@@ -1208,18 +1234,21 @@
       <c r="S5" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="T5" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="U5" s="30"/>
-      <c r="V5" s="31"/>
+      <c r="T5" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="U5" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="V5" s="30"/>
       <c r="W5" s="31"/>
       <c r="X5" s="31"/>
-      <c r="Y5" s="33" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y5" s="31"/>
+      <c r="Z5" s="33" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>2</v>
       </c>
@@ -1229,30 +1258,30 @@
       <c r="C6" s="34"/>
       <c r="D6" s="31"/>
       <c r="E6" s="35"/>
-      <c r="F6" s="31" t="s">
+      <c r="F6" s="4"/>
+      <c r="G6" s="31" t="s">
         <v>58</v>
       </c>
-      <c r="G6" s="31" t="s">
+      <c r="H6" s="31" t="s">
+        <v>59</v>
+      </c>
+      <c r="I6" s="31" t="s">
+        <v>60</v>
+      </c>
+      <c r="J6" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="K6" s="31" t="s">
         <v>56</v>
       </c>
-      <c r="H6" s="4"/>
-      <c r="I6" s="31" t="s">
-        <v>51</v>
-      </c>
-      <c r="J6" s="31" t="s">
-        <v>52</v>
-      </c>
-      <c r="K6" s="33" t="s">
-        <v>57</v>
-      </c>
-      <c r="L6" s="22"/>
-      <c r="M6" s="4"/>
+      <c r="L6" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="M6" s="22"/>
       <c r="N6" s="4"/>
-      <c r="O6" s="21"/>
-      <c r="P6" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q6" s="4" t="s">
+      <c r="O6" s="4"/>
+      <c r="P6" s="21"/>
+      <c r="Q6" s="5" t="s">
         <v>19</v>
       </c>
       <c r="R6" s="4" t="s">
@@ -1261,16 +1290,19 @@
       <c r="S6" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="T6" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="U6" s="22"/>
-      <c r="V6" s="4"/>
+      <c r="T6" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="U6" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="V6" s="22"/>
       <c r="W6" s="4"/>
       <c r="X6" s="4"/>
-      <c r="Y6" s="23"/>
-    </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Y6" s="4"/>
+      <c r="Z6" s="23"/>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>1</v>
       </c>
@@ -1280,64 +1312,67 @@
       <c r="C7" s="3"/>
       <c r="D7" s="2"/>
       <c r="E7" s="17"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="14" t="s">
+      <c r="F7" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G7" s="13"/>
+      <c r="H7" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="H7" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="I7" s="14" t="s">
-        <v>17</v>
+      <c r="I7" s="37" t="s">
+        <v>15</v>
       </c>
       <c r="J7" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="K7" s="16" t="s">
+      <c r="K7" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="L7" s="18" t="s">
+      <c r="L7" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="M7" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="M7" s="2" t="s">
+      <c r="N7" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="N7" s="2" t="s">
+      <c r="O7" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="O7" s="17" t="s">
+      <c r="P7" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="P7" s="3" t="s">
+      <c r="Q7" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="Q7" s="2" t="s">
+      <c r="R7" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="R7" s="2" t="s">
+      <c r="S7" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="S7" s="2" t="s">
+      <c r="T7" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="T7" s="16"/>
-      <c r="U7" s="18" t="s">
+      <c r="U7" s="16"/>
+      <c r="V7" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="V7" s="2" t="s">
+      <c r="W7" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="W7" s="2" t="s">
+      <c r="X7" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="X7" s="2" t="s">
+      <c r="Y7" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="Y7" s="16" t="s">
+      <c r="Z7" s="16" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>1</v>
       </c>
@@ -1347,64 +1382,67 @@
       <c r="C8" s="3"/>
       <c r="D8" s="2"/>
       <c r="E8" s="17"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="14" t="s">
-        <v>19</v>
-      </c>
+      <c r="F8" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" s="13"/>
       <c r="H8" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="I8" s="14" t="s">
-        <v>17</v>
+        <v>19</v>
+      </c>
+      <c r="I8" s="37" t="s">
+        <v>19</v>
       </c>
       <c r="J8" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="K8" s="16" t="s">
+      <c r="K8" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="L8" s="18" t="s">
+      <c r="L8" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="M8" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="M8" s="2" t="s">
+      <c r="N8" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="N8" s="2" t="s">
+      <c r="O8" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="O8" s="17" t="s">
+      <c r="P8" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="P8" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q8" s="2" t="s">
+      <c r="Q8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="R8" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="R8" s="2" t="s">
+      <c r="S8" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="S8" s="2" t="s">
+      <c r="T8" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="T8" s="16"/>
-      <c r="U8" s="18" t="s">
+      <c r="U8" s="16"/>
+      <c r="V8" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="V8" s="2" t="s">
+      <c r="W8" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="W8" s="2" t="s">
+      <c r="X8" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="X8" s="2" t="s">
+      <c r="Y8" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="Y8" s="16" t="s">
+      <c r="Z8" s="16" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>2</v>
       </c>
@@ -1414,46 +1452,49 @@
       <c r="C9" s="5"/>
       <c r="D9" s="4"/>
       <c r="E9" s="21"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="4" t="s">
-        <v>19</v>
-      </c>
+      <c r="F9" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="5"/>
       <c r="H9" s="4" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="J9" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="K9" s="6" t="s">
+      <c r="K9" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="L9" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="M9" s="4" t="s">
+      <c r="L9" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="M9" s="22" t="s">
         <v>19</v>
       </c>
       <c r="N9" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="O9" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="P9" s="5"/>
-      <c r="Q9" s="4"/>
+      <c r="O9" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="P9" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q9" s="5"/>
       <c r="R9" s="4"/>
       <c r="S9" s="4"/>
-      <c r="T9" s="6"/>
-      <c r="U9" s="22"/>
-      <c r="V9" s="4"/>
+      <c r="T9" s="4"/>
+      <c r="U9" s="6"/>
+      <c r="V9" s="22"/>
       <c r="W9" s="4"/>
       <c r="X9" s="4"/>
-      <c r="Y9" s="23"/>
-    </row>
-    <row r="10" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="Y9" s="4"/>
+      <c r="Z9" s="23"/>
+    </row>
+    <row r="10" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>0</v>
       </c>
@@ -1463,59 +1504,59 @@
       <c r="C10" s="24"/>
       <c r="D10" s="25"/>
       <c r="E10" s="27"/>
-      <c r="F10" s="24"/>
-      <c r="G10" s="25" t="s">
+      <c r="F10" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="G10" s="24"/>
+      <c r="H10" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="H10" s="25" t="s">
-        <v>19</v>
-      </c>
       <c r="I10" s="25" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J10" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="K10" s="26" t="s">
+      <c r="K10" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="L10" s="28" t="s">
-        <v>19</v>
-      </c>
-      <c r="M10" s="25" t="s">
-        <v>14</v>
+      <c r="L10" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="M10" s="28" t="s">
+        <v>19</v>
       </c>
       <c r="N10" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="O10" s="27" t="s">
+      <c r="O10" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="P10" s="24"/>
-      <c r="Q10" s="25"/>
+      <c r="P10" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q10" s="24"/>
       <c r="R10" s="25"/>
       <c r="S10" s="25"/>
-      <c r="T10" s="26"/>
-      <c r="U10" s="28"/>
-      <c r="V10" s="25"/>
+      <c r="T10" s="25"/>
+      <c r="U10" s="26"/>
+      <c r="V10" s="28"/>
       <c r="W10" s="25"/>
       <c r="X10" s="25"/>
-      <c r="Y10" s="29"/>
-    </row>
-    <row r="11" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="H11" s="25" t="s">
+      <c r="Y10" s="25"/>
+      <c r="Z10" s="29"/>
+    </row>
+    <row r="11" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F11" s="25" t="s">
         <v>19</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="U3:Y3"/>
-    <mergeCell ref="P3:T3"/>
-    <mergeCell ref="P2:T2"/>
+  <mergeCells count="4">
+    <mergeCell ref="V3:Z3"/>
+    <mergeCell ref="Q3:U3"/>
+    <mergeCell ref="Q2:U2"/>
     <mergeCell ref="C2:E2"/>
-    <mergeCell ref="L3:O3"/>
-    <mergeCell ref="F2:O2"/>
-    <mergeCell ref="F3:K3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="8" scale="82" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -1535,7 +1576,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -1543,7 +1584,7 @@
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.25">
@@ -1593,7 +1634,7 @@
   <sheetData>
     <row r="2" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D2" t="s">
         <v>3</v>
@@ -1607,17 +1648,17 @@
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/reestr.xlsx
+++ b/reestr.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="68">
   <si>
     <t>Спортзал</t>
   </si>
@@ -172,9 +172,6 @@
     <t>Стены</t>
   </si>
   <si>
-    <t>2.1-Пт</t>
-  </si>
-  <si>
     <t>Монтаж</t>
   </si>
   <si>
@@ -215,6 +212,24 @@
   </si>
   <si>
     <t xml:space="preserve">ШП.1  </t>
+  </si>
+  <si>
+    <t>3.2-Пл</t>
+  </si>
+  <si>
+    <t>3.3-Пл</t>
+  </si>
+  <si>
+    <t>Стяжа</t>
+  </si>
+  <si>
+    <t>Налив</t>
+  </si>
+  <si>
+    <t>Плитка</t>
+  </si>
+  <si>
+    <t>3.1-Пт</t>
   </si>
 </sst>
 </file>
@@ -591,7 +606,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -687,43 +702,10 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -743,6 +725,36 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1046,31 +1058,31 @@
     <row r="2" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="9"/>
-      <c r="C2" s="45" t="s">
+      <c r="C2" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="46"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="53" t="s">
+      <c r="D2" s="51"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
-      <c r="K2" s="48"/>
-      <c r="L2" s="48"/>
-      <c r="M2" s="48"/>
-      <c r="N2" s="48"/>
-      <c r="O2" s="48"/>
-      <c r="P2" s="49"/>
-      <c r="Q2" s="44" t="s">
+      <c r="G2" s="37"/>
+      <c r="H2" s="37"/>
+      <c r="I2" s="37"/>
+      <c r="J2" s="37"/>
+      <c r="K2" s="37"/>
+      <c r="L2" s="37"/>
+      <c r="M2" s="37"/>
+      <c r="N2" s="37"/>
+      <c r="O2" s="37"/>
+      <c r="P2" s="38"/>
+      <c r="Q2" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="R2" s="39"/>
-      <c r="S2" s="39"/>
-      <c r="T2" s="39"/>
-      <c r="U2" s="40"/>
+      <c r="R2" s="44"/>
+      <c r="S2" s="44"/>
+      <c r="T2" s="44"/>
+      <c r="U2" s="45"/>
       <c r="V2" s="10"/>
       <c r="W2" s="10"/>
       <c r="X2" s="10"/>
@@ -1081,55 +1093,61 @@
       <c r="B3" s="9"/>
       <c r="C3" s="11"/>
       <c r="D3" s="12"/>
-      <c r="E3" s="36"/>
-      <c r="F3" s="51" t="s">
+      <c r="E3" s="35"/>
+      <c r="F3" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="51"/>
-      <c r="K3" s="51"/>
-      <c r="L3" s="52"/>
-      <c r="M3" s="50" t="s">
+      <c r="G3" s="40"/>
+      <c r="H3" s="40"/>
+      <c r="I3" s="40"/>
+      <c r="J3" s="40"/>
+      <c r="K3" s="40"/>
+      <c r="L3" s="41"/>
+      <c r="M3" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="N3" s="50"/>
-      <c r="O3" s="50"/>
-      <c r="P3" s="50"/>
-      <c r="Q3" s="41" t="s">
+      <c r="N3" s="39"/>
+      <c r="O3" s="39"/>
+      <c r="P3" s="39"/>
+      <c r="Q3" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="R3" s="42"/>
-      <c r="S3" s="42"/>
-      <c r="T3" s="42"/>
-      <c r="U3" s="43"/>
-      <c r="V3" s="38" t="s">
+      <c r="R3" s="47"/>
+      <c r="S3" s="47"/>
+      <c r="T3" s="47"/>
+      <c r="U3" s="48"/>
+      <c r="V3" s="43" t="s">
         <v>36</v>
       </c>
-      <c r="W3" s="39"/>
-      <c r="X3" s="39"/>
-      <c r="Y3" s="39"/>
-      <c r="Z3" s="40"/>
+      <c r="W3" s="44"/>
+      <c r="X3" s="44"/>
+      <c r="Y3" s="44"/>
+      <c r="Z3" s="45"/>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="C4" s="15"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="17"/>
+      <c r="C4" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E4" s="17" t="s">
+        <v>66</v>
+      </c>
       <c r="F4" s="14" t="s">
         <v>6</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H4" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="I4" s="37" t="s">
+      <c r="I4" s="36" t="s">
         <v>37</v>
       </c>
       <c r="J4" s="14" t="s">
@@ -1166,7 +1184,7 @@
         <v>9</v>
       </c>
       <c r="U4" s="16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="V4" s="18" t="s">
         <v>6</v>
@@ -1201,10 +1219,10 @@
         <v>40</v>
       </c>
       <c r="F5" s="31" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G5" s="34" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>39</v>
@@ -1213,13 +1231,13 @@
         <v>39</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K5" s="31" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="L5" s="32" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M5" s="22"/>
       <c r="N5" s="4"/>
@@ -1245,7 +1263,7 @@
       <c r="X5" s="31"/>
       <c r="Y5" s="31"/>
       <c r="Z5" s="33" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
@@ -1255,27 +1273,33 @@
       <c r="B6" s="20">
         <v>1.032</v>
       </c>
-      <c r="C6" s="34"/>
-      <c r="D6" s="31"/>
-      <c r="E6" s="35"/>
+      <c r="C6" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="31" t="s">
+        <v>62</v>
+      </c>
+      <c r="E6" s="31" t="s">
+        <v>63</v>
+      </c>
       <c r="F6" s="4"/>
       <c r="G6" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="H6" s="31" t="s">
         <v>58</v>
       </c>
-      <c r="H6" s="31" t="s">
+      <c r="I6" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="I6" s="31" t="s">
-        <v>60</v>
-      </c>
       <c r="J6" s="31" t="s">
+        <v>54</v>
+      </c>
+      <c r="K6" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="K6" s="31" t="s">
-        <v>56</v>
-      </c>
       <c r="L6" s="33" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M6" s="22"/>
       <c r="N6" s="4"/>
@@ -1293,8 +1317,8 @@
       <c r="T6" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="U6" s="6" t="s">
-        <v>48</v>
+      <c r="U6" s="32" t="s">
+        <v>67</v>
       </c>
       <c r="V6" s="22"/>
       <c r="W6" s="4"/>
@@ -1319,7 +1343,7 @@
       <c r="H7" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="I7" s="37" t="s">
+      <c r="I7" s="36" t="s">
         <v>15</v>
       </c>
       <c r="J7" s="14" t="s">
@@ -1389,7 +1413,7 @@
       <c r="H8" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="I8" s="37" t="s">
+      <c r="I8" s="36" t="s">
         <v>19</v>
       </c>
       <c r="J8" s="14" t="s">

--- a/reestr.xlsx
+++ b/reestr.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16665" windowHeight="8130"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16665" windowHeight="8130" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Школа № 1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="86">
   <si>
     <t>Спортзал</t>
   </si>
@@ -157,15 +157,6 @@
     <t>Этаж</t>
   </si>
   <si>
-    <t>1-Этаж</t>
-  </si>
-  <si>
-    <t>2-Этаж</t>
-  </si>
-  <si>
-    <t>3-Этаж</t>
-  </si>
-  <si>
     <t>№ секции</t>
   </si>
   <si>
@@ -230,6 +221,69 @@
   </si>
   <si>
     <t>3.1-Пт</t>
+  </si>
+  <si>
+    <t>Шт</t>
+  </si>
+  <si>
+    <t>шп. Фин.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1-Этаж коридор </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1-Этаж комнаты </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2-Этаж коридор </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2-Этаж комнаты </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2-Этаж спортзал </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3-Этаж коридор </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3-Этаж комнаты </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3-Этаж спортзал </t>
+  </si>
+  <si>
+    <t>стяжка</t>
+  </si>
+  <si>
+    <t>Шпаклевка</t>
+  </si>
+  <si>
+    <t>1.П</t>
+  </si>
+  <si>
+    <t>1.Шт</t>
+  </si>
+  <si>
+    <t>2.Шт-Пт-2Э</t>
+  </si>
+  <si>
+    <t>1.Шт-Ст-2Э</t>
+  </si>
+  <si>
+    <t>3.Шт-Пт-3Э</t>
+  </si>
+  <si>
+    <t>Лестница</t>
+  </si>
+  <si>
+    <t>Штукатука стен</t>
+  </si>
+  <si>
+    <t>шпаклевка потолка</t>
+  </si>
+  <si>
+    <t>Штукатука потолка с сеткой пролетка и каждого этажа</t>
   </si>
 </sst>
 </file>
@@ -239,7 +293,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -255,8 +309,16 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFFFF00"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -275,8 +337,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="25">
+  <borders count="26">
     <border>
       <left/>
       <right/>
@@ -602,11 +676,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -726,6 +813,24 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1058,11 +1163,11 @@
     <row r="2" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="9"/>
-      <c r="C2" s="50" t="s">
+      <c r="C2" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="51"/>
-      <c r="E2" s="52"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="70"/>
       <c r="F2" s="42" t="s">
         <v>4</v>
       </c>
@@ -1076,13 +1181,13 @@
       <c r="N2" s="37"/>
       <c r="O2" s="37"/>
       <c r="P2" s="38"/>
-      <c r="Q2" s="49" t="s">
+      <c r="Q2" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="R2" s="44"/>
-      <c r="S2" s="44"/>
-      <c r="T2" s="44"/>
-      <c r="U2" s="45"/>
+      <c r="R2" s="62"/>
+      <c r="S2" s="62"/>
+      <c r="T2" s="62"/>
+      <c r="U2" s="63"/>
       <c r="V2" s="10"/>
       <c r="W2" s="10"/>
       <c r="X2" s="10"/>
@@ -1109,20 +1214,20 @@
       <c r="N3" s="39"/>
       <c r="O3" s="39"/>
       <c r="P3" s="39"/>
-      <c r="Q3" s="46" t="s">
+      <c r="Q3" s="64" t="s">
         <v>5</v>
       </c>
-      <c r="R3" s="47"/>
-      <c r="S3" s="47"/>
-      <c r="T3" s="47"/>
-      <c r="U3" s="48"/>
-      <c r="V3" s="43" t="s">
+      <c r="R3" s="65"/>
+      <c r="S3" s="65"/>
+      <c r="T3" s="65"/>
+      <c r="U3" s="66"/>
+      <c r="V3" s="61" t="s">
         <v>36</v>
       </c>
-      <c r="W3" s="44"/>
-      <c r="X3" s="44"/>
-      <c r="Y3" s="44"/>
-      <c r="Z3" s="45"/>
+      <c r="W3" s="62"/>
+      <c r="X3" s="62"/>
+      <c r="Y3" s="62"/>
+      <c r="Z3" s="63"/>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -1130,19 +1235,19 @@
         <v>41</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F4" s="14" t="s">
         <v>6</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H4" s="14" t="s">
         <v>37</v>
@@ -1184,7 +1289,7 @@
         <v>9</v>
       </c>
       <c r="U4" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="V4" s="18" t="s">
         <v>6</v>
@@ -1219,10 +1324,10 @@
         <v>40</v>
       </c>
       <c r="F5" s="31" t="s">
+        <v>50</v>
+      </c>
+      <c r="G5" s="34" t="s">
         <v>53</v>
-      </c>
-      <c r="G5" s="34" t="s">
-        <v>56</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>39</v>
@@ -1231,13 +1336,13 @@
         <v>39</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="K5" s="31" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="L5" s="32" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="M5" s="22"/>
       <c r="N5" s="4"/>
@@ -1263,7 +1368,7 @@
       <c r="X5" s="31"/>
       <c r="Y5" s="31"/>
       <c r="Z5" s="33" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
@@ -1277,29 +1382,29 @@
         <v>19</v>
       </c>
       <c r="D6" s="31" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E6" s="31" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F6" s="4"/>
       <c r="G6" s="31" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="H6" s="31" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="I6" s="31" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="J6" s="31" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="K6" s="31" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="L6" s="33" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="M6" s="22"/>
       <c r="N6" s="4"/>
@@ -1318,7 +1423,7 @@
         <v>19</v>
       </c>
       <c r="U6" s="32" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="V6" s="22"/>
       <c r="W6" s="4"/>
@@ -1600,7 +1705,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -1608,7 +1713,7 @@
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.25">
@@ -1653,39 +1758,214 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:H6"/>
+  <dimension ref="B2:J19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="18.28515625" customWidth="1"/>
+    <col min="6" max="6" width="11.28515625" customWidth="1"/>
+    <col min="10" max="10" width="13.5703125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B2" t="s">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B2" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="D2" t="s">
+      <c r="C2" s="43"/>
+      <c r="D2" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="F2" t="s">
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="43"/>
+      <c r="I2" s="43"/>
+      <c r="J2" s="43" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
-        <v>45</v>
+    <row r="3" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="43"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="47" t="s">
+        <v>75</v>
+      </c>
+      <c r="E3" s="47"/>
+      <c r="F3" s="47" t="s">
+        <v>65</v>
+      </c>
+      <c r="G3" s="47" t="s">
+        <v>7</v>
+      </c>
+      <c r="H3" s="47" t="s">
+        <v>66</v>
+      </c>
+      <c r="I3" s="47"/>
+      <c r="J3" s="47" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="4" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="45" t="s">
+        <v>67</v>
+      </c>
+      <c r="C4" s="48"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="49" t="s">
+        <v>78</v>
+      </c>
+      <c r="G4" s="49"/>
+      <c r="H4" s="49"/>
+      <c r="I4" s="49"/>
+      <c r="J4" s="50" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B5" s="46" t="s">
+        <v>68</v>
+      </c>
+      <c r="C5" s="51"/>
+      <c r="D5" s="43"/>
+      <c r="E5" s="43"/>
+      <c r="F5" s="49" t="s">
+        <v>78</v>
+      </c>
+      <c r="G5" s="43"/>
+      <c r="H5" s="43"/>
+      <c r="I5" s="43"/>
+      <c r="J5" s="59"/>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B6" s="46"/>
+      <c r="C6" s="51"/>
+      <c r="D6" s="43"/>
+      <c r="E6" s="43"/>
+      <c r="F6" s="43"/>
+      <c r="G6" s="43"/>
+      <c r="H6" s="43"/>
+      <c r="I6" s="43"/>
+      <c r="J6" s="52"/>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B7" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="C7" s="51"/>
+      <c r="D7" s="58"/>
+      <c r="E7" s="43"/>
+      <c r="F7" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="G7" s="43"/>
+      <c r="H7" s="43"/>
+      <c r="I7" s="43"/>
+      <c r="J7" s="52" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B8" s="45" t="s">
+        <v>70</v>
+      </c>
+      <c r="C8" s="53"/>
+      <c r="D8" s="58"/>
+      <c r="E8" s="44"/>
+      <c r="F8" s="44"/>
+      <c r="G8" s="44"/>
+      <c r="H8" s="44"/>
+      <c r="I8" s="44"/>
+      <c r="J8" s="54"/>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B9" s="46" t="s">
+        <v>71</v>
+      </c>
+      <c r="C9" s="51"/>
+      <c r="D9" s="43"/>
+      <c r="E9" s="43"/>
+      <c r="F9" s="43"/>
+      <c r="G9" s="43"/>
+      <c r="H9" s="43"/>
+      <c r="I9" s="43"/>
+      <c r="J9" s="52"/>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B10" s="46"/>
+      <c r="C10" s="51"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="43"/>
+      <c r="F10" s="43"/>
+      <c r="G10" s="43"/>
+      <c r="H10" s="43"/>
+      <c r="I10" s="43"/>
+      <c r="J10" s="52"/>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B11" s="45" t="s">
+        <v>72</v>
+      </c>
+      <c r="C11" s="53"/>
+      <c r="D11" s="58"/>
+      <c r="E11" s="44"/>
+      <c r="F11" s="60"/>
+      <c r="G11" s="44"/>
+      <c r="H11" s="44"/>
+      <c r="I11" s="44"/>
+      <c r="J11" s="52" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B12" s="46" t="s">
+        <v>73</v>
+      </c>
+      <c r="C12" s="51"/>
+      <c r="D12" s="58"/>
+      <c r="E12" s="43"/>
+      <c r="F12" s="60"/>
+      <c r="G12" s="43"/>
+      <c r="H12" s="43"/>
+      <c r="I12" s="43"/>
+      <c r="J12" s="52"/>
+    </row>
+    <row r="13" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="45" t="s">
+        <v>74</v>
+      </c>
+      <c r="C13" s="55"/>
+      <c r="D13" s="56"/>
+      <c r="E13" s="56"/>
+      <c r="F13" s="56"/>
+      <c r="G13" s="56"/>
+      <c r="H13" s="56"/>
+      <c r="I13" s="56"/>
+      <c r="J13" s="57"/>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
+        <v>84</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/reestr.xlsx
+++ b/reestr.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="99">
   <si>
     <t>Спортзал</t>
   </si>
@@ -284,6 +284,45 @@
   </si>
   <si>
     <t>Штукатука потолка с сеткой пролетка и каждого этажа</t>
+  </si>
+  <si>
+    <t>сделать</t>
+  </si>
+  <si>
+    <t>НЗ</t>
+  </si>
+  <si>
+    <t>Заливка диафграма</t>
+  </si>
+  <si>
+    <t>Еще отопление</t>
+  </si>
+  <si>
+    <t>3 этаж</t>
+  </si>
+  <si>
+    <t>заливка</t>
+  </si>
+  <si>
+    <t>2 этаж</t>
+  </si>
+  <si>
+    <t>кроме спортазала</t>
+  </si>
+  <si>
+    <t>Штукатурка</t>
+  </si>
+  <si>
+    <t>шпаклевка</t>
+  </si>
+  <si>
+    <t>2.Шт-Ст-3Э</t>
+  </si>
+  <si>
+    <t>изоляу</t>
+  </si>
+  <si>
+    <t>1.Из-Пл</t>
   </si>
 </sst>
 </file>
@@ -293,7 +332,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -309,16 +348,8 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFFFF00"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -349,6 +380,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="26">
     <border>
@@ -693,7 +736,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -830,7 +873,17 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1163,11 +1216,11 @@
     <row r="2" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="9"/>
-      <c r="C2" s="68" t="s">
+      <c r="C2" s="76" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="69"/>
-      <c r="E2" s="70"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="78"/>
       <c r="F2" s="42" t="s">
         <v>4</v>
       </c>
@@ -1181,13 +1234,13 @@
       <c r="N2" s="37"/>
       <c r="O2" s="37"/>
       <c r="P2" s="38"/>
-      <c r="Q2" s="67" t="s">
+      <c r="Q2" s="75" t="s">
         <v>5</v>
       </c>
-      <c r="R2" s="62"/>
-      <c r="S2" s="62"/>
-      <c r="T2" s="62"/>
-      <c r="U2" s="63"/>
+      <c r="R2" s="70"/>
+      <c r="S2" s="70"/>
+      <c r="T2" s="70"/>
+      <c r="U2" s="71"/>
       <c r="V2" s="10"/>
       <c r="W2" s="10"/>
       <c r="X2" s="10"/>
@@ -1214,20 +1267,20 @@
       <c r="N3" s="39"/>
       <c r="O3" s="39"/>
       <c r="P3" s="39"/>
-      <c r="Q3" s="64" t="s">
+      <c r="Q3" s="72" t="s">
         <v>5</v>
       </c>
-      <c r="R3" s="65"/>
-      <c r="S3" s="65"/>
-      <c r="T3" s="65"/>
-      <c r="U3" s="66"/>
-      <c r="V3" s="61" t="s">
+      <c r="R3" s="73"/>
+      <c r="S3" s="73"/>
+      <c r="T3" s="73"/>
+      <c r="U3" s="74"/>
+      <c r="V3" s="69" t="s">
         <v>36</v>
       </c>
-      <c r="W3" s="62"/>
-      <c r="X3" s="62"/>
-      <c r="Y3" s="62"/>
-      <c r="Z3" s="63"/>
+      <c r="W3" s="70"/>
+      <c r="X3" s="70"/>
+      <c r="Y3" s="70"/>
+      <c r="Z3" s="71"/>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -1694,62 +1747,213 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:E10"/>
+  <dimension ref="B2:F22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.28515625" customWidth="1"/>
+    <col min="3" max="3" width="12.42578125" customWidth="1"/>
+    <col min="4" max="4" width="13.140625" customWidth="1"/>
+    <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C2" t="s">
+    <row r="2" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B2" s="43"/>
+      <c r="C2" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="43" t="s">
         <v>44</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="43"/>
+      <c r="F2" s="43" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B3" t="s">
+    <row r="3" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B3" s="43"/>
+      <c r="C3" s="43" t="s">
+        <v>91</v>
+      </c>
+      <c r="D3" s="43" t="s">
+        <v>94</v>
+      </c>
+      <c r="E3" s="43" t="s">
+        <v>95</v>
+      </c>
+      <c r="F3" s="43"/>
+    </row>
+    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B4" s="43" t="s">
+        <v>92</v>
+      </c>
+      <c r="C4" s="43"/>
+      <c r="D4" s="43"/>
+      <c r="E4" s="43"/>
+      <c r="F4" s="43"/>
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B5" s="43" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B4">
+      <c r="C5" s="43"/>
+      <c r="D5" s="43"/>
+      <c r="E5" s="43"/>
+      <c r="F5" s="43"/>
+    </row>
+    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B6" s="43">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B5">
+      <c r="C6" s="63"/>
+      <c r="D6" s="65"/>
+      <c r="E6" s="65"/>
+      <c r="F6" s="43"/>
+    </row>
+    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B7" s="43">
         <v>2</v>
       </c>
-    </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B6">
+      <c r="C7" s="63"/>
+      <c r="D7" s="65"/>
+      <c r="E7" s="65"/>
+      <c r="F7" s="43"/>
+    </row>
+    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B8" s="43">
         <v>3</v>
       </c>
-    </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B7">
+      <c r="C8" s="63"/>
+      <c r="D8" s="65"/>
+      <c r="E8" s="65"/>
+      <c r="F8" s="43"/>
+    </row>
+    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B9" s="43">
         <v>4</v>
       </c>
-    </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B8">
+      <c r="C9" s="63"/>
+      <c r="D9" s="63"/>
+      <c r="E9" s="63"/>
+      <c r="F9" s="43"/>
+    </row>
+    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B10" s="43">
         <v>5</v>
       </c>
-    </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B9">
+      <c r="C10" s="63"/>
+      <c r="D10" s="63"/>
+      <c r="E10" s="63"/>
+      <c r="F10" s="43"/>
+    </row>
+    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B11" s="43">
         <v>6</v>
       </c>
-    </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B10">
+      <c r="C11" s="63"/>
+      <c r="D11" s="63"/>
+      <c r="E11" s="63"/>
+      <c r="F11" s="43"/>
+    </row>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B12" s="43">
         <v>7</v>
       </c>
+      <c r="C12" s="63"/>
+      <c r="D12" s="63"/>
+      <c r="E12" s="63"/>
+      <c r="F12" s="43"/>
+    </row>
+    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B13" s="43" t="s">
+        <v>90</v>
+      </c>
+      <c r="C13" s="43"/>
+      <c r="D13" s="43"/>
+      <c r="E13" s="43"/>
+      <c r="F13" s="43"/>
+    </row>
+    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B14" s="43" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" s="43"/>
+      <c r="D14" s="43"/>
+      <c r="E14" s="43"/>
+      <c r="F14" s="43"/>
+    </row>
+    <row r="15" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B15" s="43">
+        <v>1</v>
+      </c>
+      <c r="C15" s="63"/>
+      <c r="D15" s="65"/>
+      <c r="E15" s="65"/>
+      <c r="F15" s="43"/>
+    </row>
+    <row r="16" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B16" s="43">
+        <v>2</v>
+      </c>
+      <c r="C16" s="63"/>
+      <c r="D16" s="65"/>
+      <c r="E16" s="65"/>
+      <c r="F16" s="43"/>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B17" s="43">
+        <v>3</v>
+      </c>
+      <c r="C17" s="63"/>
+      <c r="D17" s="65"/>
+      <c r="E17" s="65"/>
+      <c r="F17" s="43"/>
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B18" s="43">
+        <v>4</v>
+      </c>
+      <c r="C18" s="63"/>
+      <c r="D18" s="63"/>
+      <c r="E18" s="63"/>
+      <c r="F18" s="43"/>
+    </row>
+    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B19" s="43">
+        <v>5</v>
+      </c>
+      <c r="C19" s="63"/>
+      <c r="D19" s="63"/>
+      <c r="E19" s="63"/>
+      <c r="F19" s="43"/>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B20" s="43">
+        <v>6</v>
+      </c>
+      <c r="C20" s="63"/>
+      <c r="D20" s="63"/>
+      <c r="E20" s="63"/>
+      <c r="F20" s="43"/>
+    </row>
+    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B21" s="43">
+        <v>7</v>
+      </c>
+      <c r="C21" s="63"/>
+      <c r="D21" s="63"/>
+      <c r="E21" s="63"/>
+      <c r="F21" s="43"/>
+    </row>
+    <row r="22" spans="2:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="B22" s="43"/>
+      <c r="C22" s="64" t="s">
+        <v>93</v>
+      </c>
+      <c r="D22" s="64" t="s">
+        <v>93</v>
+      </c>
+      <c r="E22" s="43"/>
+      <c r="F22" s="43"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1758,7 +1962,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:J19"/>
+  <dimension ref="B2:J26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.28515625" customWidth="1"/>
@@ -1787,7 +1991,9 @@
     </row>
     <row r="3" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="43"/>
-      <c r="C3" s="47"/>
+      <c r="C3" s="47" t="s">
+        <v>97</v>
+      </c>
       <c r="D3" s="47" t="s">
         <v>75</v>
       </c>
@@ -1810,13 +2016,15 @@
       <c r="B4" s="45" t="s">
         <v>67</v>
       </c>
-      <c r="C4" s="48"/>
-      <c r="D4" s="49"/>
+      <c r="C4" s="48" t="s">
+        <v>98</v>
+      </c>
+      <c r="D4" s="61"/>
       <c r="E4" s="49"/>
-      <c r="F4" s="49" t="s">
+      <c r="F4" s="68" t="s">
         <v>78</v>
       </c>
-      <c r="G4" s="49"/>
+      <c r="G4" s="61"/>
       <c r="H4" s="49"/>
       <c r="I4" s="49"/>
       <c r="J4" s="50" t="s">
@@ -1827,18 +2035,20 @@
       <c r="B5" s="46" t="s">
         <v>68</v>
       </c>
-      <c r="C5" s="51"/>
-      <c r="D5" s="43"/>
+      <c r="C5" s="48" t="s">
+        <v>98</v>
+      </c>
+      <c r="D5" s="58"/>
       <c r="E5" s="43"/>
-      <c r="F5" s="49" t="s">
+      <c r="F5" s="68" t="s">
         <v>78</v>
       </c>
-      <c r="G5" s="43"/>
+      <c r="G5" s="58"/>
       <c r="H5" s="43"/>
       <c r="I5" s="43"/>
       <c r="J5" s="59"/>
     </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="46"/>
       <c r="C6" s="51"/>
       <c r="D6" s="43"/>
@@ -1849,17 +2059,19 @@
       <c r="I6" s="43"/>
       <c r="J6" s="52"/>
     </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="46" t="s">
         <v>69</v>
       </c>
-      <c r="C7" s="51"/>
+      <c r="C7" s="48" t="s">
+        <v>98</v>
+      </c>
       <c r="D7" s="58"/>
       <c r="E7" s="43"/>
-      <c r="F7" s="43" t="s">
+      <c r="F7" s="67" t="s">
         <v>80</v>
       </c>
-      <c r="G7" s="43"/>
+      <c r="G7" s="58"/>
       <c r="H7" s="43"/>
       <c r="I7" s="43"/>
       <c r="J7" s="52" t="s">
@@ -1870,11 +2082,13 @@
       <c r="B8" s="45" t="s">
         <v>70</v>
       </c>
-      <c r="C8" s="53"/>
+      <c r="C8" s="48" t="s">
+        <v>98</v>
+      </c>
       <c r="D8" s="58"/>
       <c r="E8" s="44"/>
       <c r="F8" s="44"/>
-      <c r="G8" s="44"/>
+      <c r="G8" s="58"/>
       <c r="H8" s="44"/>
       <c r="I8" s="44"/>
       <c r="J8" s="54"/>
@@ -1883,11 +2097,13 @@
       <c r="B9" s="46" t="s">
         <v>71</v>
       </c>
-      <c r="C9" s="51"/>
+      <c r="C9" s="51" t="s">
+        <v>19</v>
+      </c>
       <c r="D9" s="43"/>
       <c r="E9" s="43"/>
       <c r="F9" s="43"/>
-      <c r="G9" s="43"/>
+      <c r="G9" s="58"/>
       <c r="H9" s="43"/>
       <c r="I9" s="43"/>
       <c r="J9" s="52"/>
@@ -1907,11 +2123,15 @@
       <c r="B11" s="45" t="s">
         <v>72</v>
       </c>
-      <c r="C11" s="53"/>
+      <c r="C11" s="53" t="s">
+        <v>19</v>
+      </c>
       <c r="D11" s="58"/>
       <c r="E11" s="44"/>
-      <c r="F11" s="60"/>
-      <c r="G11" s="44"/>
+      <c r="F11" s="66" t="s">
+        <v>96</v>
+      </c>
+      <c r="G11" s="58"/>
       <c r="H11" s="44"/>
       <c r="I11" s="44"/>
       <c r="J11" s="52" t="s">
@@ -1922,11 +2142,15 @@
       <c r="B12" s="46" t="s">
         <v>73</v>
       </c>
-      <c r="C12" s="51"/>
+      <c r="C12" s="51" t="s">
+        <v>19</v>
+      </c>
       <c r="D12" s="58"/>
       <c r="E12" s="43"/>
-      <c r="F12" s="60"/>
-      <c r="G12" s="43"/>
+      <c r="F12" s="66" t="s">
+        <v>96</v>
+      </c>
+      <c r="G12" s="58"/>
       <c r="H12" s="43"/>
       <c r="I12" s="43"/>
       <c r="J12" s="52"/>
@@ -1935,11 +2159,13 @@
       <c r="B13" s="45" t="s">
         <v>74</v>
       </c>
-      <c r="C13" s="55"/>
-      <c r="D13" s="56"/>
+      <c r="C13" s="55" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="60"/>
       <c r="E13" s="56"/>
-      <c r="F13" s="56"/>
-      <c r="G13" s="56"/>
+      <c r="F13" s="60"/>
+      <c r="G13" s="60"/>
       <c r="H13" s="56"/>
       <c r="I13" s="56"/>
       <c r="J13" s="57"/>
@@ -1949,19 +2175,40 @@
         <v>82</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>84</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B21" s="62"/>
+      <c r="C21" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B24" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B25" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B26" t="s">
+        <v>89</v>
       </c>
     </row>
   </sheetData>

--- a/reestr.xlsx
+++ b/reestr.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="106">
   <si>
     <t>Спортзал</t>
   </si>
@@ -323,6 +323,27 @@
   </si>
   <si>
     <t>1.Из-Пл</t>
+  </si>
+  <si>
+    <t>пленка</t>
+  </si>
+  <si>
+    <t>3.Шт-Ст</t>
+  </si>
+  <si>
+    <t>1.Пл-Пл</t>
+  </si>
+  <si>
+    <t>2.1-пл-3э</t>
+  </si>
+  <si>
+    <t>1.1-пл-2э</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1.СКБ-Пл</t>
+  </si>
+  <si>
+    <t>4.СКБ-Пт</t>
   </si>
 </sst>
 </file>
@@ -349,7 +370,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -376,12 +397,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -393,7 +408,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="26">
+  <borders count="28">
     <border>
       <left/>
       <right/>
@@ -732,11 +747,35 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -867,23 +906,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="26" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1216,11 +1257,11 @@
     <row r="2" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="9"/>
-      <c r="C2" s="76" t="s">
+      <c r="C2" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="77"/>
-      <c r="E2" s="78"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="80"/>
       <c r="F2" s="42" t="s">
         <v>4</v>
       </c>
@@ -1234,13 +1275,13 @@
       <c r="N2" s="37"/>
       <c r="O2" s="37"/>
       <c r="P2" s="38"/>
-      <c r="Q2" s="75" t="s">
+      <c r="Q2" s="77" t="s">
         <v>5</v>
       </c>
-      <c r="R2" s="70"/>
-      <c r="S2" s="70"/>
-      <c r="T2" s="70"/>
-      <c r="U2" s="71"/>
+      <c r="R2" s="72"/>
+      <c r="S2" s="72"/>
+      <c r="T2" s="72"/>
+      <c r="U2" s="73"/>
       <c r="V2" s="10"/>
       <c r="W2" s="10"/>
       <c r="X2" s="10"/>
@@ -1267,20 +1308,20 @@
       <c r="N3" s="39"/>
       <c r="O3" s="39"/>
       <c r="P3" s="39"/>
-      <c r="Q3" s="72" t="s">
+      <c r="Q3" s="74" t="s">
         <v>5</v>
       </c>
-      <c r="R3" s="73"/>
-      <c r="S3" s="73"/>
-      <c r="T3" s="73"/>
-      <c r="U3" s="74"/>
-      <c r="V3" s="69" t="s">
+      <c r="R3" s="75"/>
+      <c r="S3" s="75"/>
+      <c r="T3" s="75"/>
+      <c r="U3" s="76"/>
+      <c r="V3" s="71" t="s">
         <v>36</v>
       </c>
-      <c r="W3" s="70"/>
-      <c r="X3" s="70"/>
-      <c r="Y3" s="70"/>
-      <c r="Z3" s="71"/>
+      <c r="W3" s="72"/>
+      <c r="X3" s="72"/>
+      <c r="Y3" s="72"/>
+      <c r="Z3" s="73"/>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -1804,63 +1845,63 @@
       <c r="B6" s="43">
         <v>1</v>
       </c>
-      <c r="C6" s="63"/>
-      <c r="D6" s="65"/>
-      <c r="E6" s="65"/>
+      <c r="C6" s="61"/>
+      <c r="D6" s="63"/>
+      <c r="E6" s="63"/>
       <c r="F6" s="43"/>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B7" s="43">
         <v>2</v>
       </c>
-      <c r="C7" s="63"/>
-      <c r="D7" s="65"/>
-      <c r="E7" s="65"/>
+      <c r="C7" s="61"/>
+      <c r="D7" s="63"/>
+      <c r="E7" s="63"/>
       <c r="F7" s="43"/>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B8" s="43">
         <v>3</v>
       </c>
-      <c r="C8" s="63"/>
-      <c r="D8" s="65"/>
-      <c r="E8" s="65"/>
+      <c r="C8" s="61"/>
+      <c r="D8" s="63"/>
+      <c r="E8" s="63"/>
       <c r="F8" s="43"/>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B9" s="43">
         <v>4</v>
       </c>
-      <c r="C9" s="63"/>
-      <c r="D9" s="63"/>
-      <c r="E9" s="63"/>
+      <c r="C9" s="61"/>
+      <c r="D9" s="61"/>
+      <c r="E9" s="61"/>
       <c r="F9" s="43"/>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B10" s="43">
         <v>5</v>
       </c>
-      <c r="C10" s="63"/>
-      <c r="D10" s="63"/>
-      <c r="E10" s="63"/>
+      <c r="C10" s="61"/>
+      <c r="D10" s="61"/>
+      <c r="E10" s="61"/>
       <c r="F10" s="43"/>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B11" s="43">
         <v>6</v>
       </c>
-      <c r="C11" s="63"/>
-      <c r="D11" s="63"/>
-      <c r="E11" s="63"/>
+      <c r="C11" s="61"/>
+      <c r="D11" s="61"/>
+      <c r="E11" s="61"/>
       <c r="F11" s="43"/>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B12" s="43">
         <v>7</v>
       </c>
-      <c r="C12" s="63"/>
-      <c r="D12" s="63"/>
-      <c r="E12" s="63"/>
+      <c r="C12" s="61"/>
+      <c r="D12" s="61"/>
+      <c r="E12" s="61"/>
       <c r="F12" s="43"/>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.25">
@@ -1885,71 +1926,71 @@
       <c r="B15" s="43">
         <v>1</v>
       </c>
-      <c r="C15" s="63"/>
-      <c r="D15" s="65"/>
-      <c r="E15" s="65"/>
+      <c r="C15" s="61"/>
+      <c r="D15" s="63"/>
+      <c r="E15" s="63"/>
       <c r="F15" s="43"/>
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B16" s="43">
         <v>2</v>
       </c>
-      <c r="C16" s="63"/>
-      <c r="D16" s="65"/>
-      <c r="E16" s="65"/>
+      <c r="C16" s="61"/>
+      <c r="D16" s="63"/>
+      <c r="E16" s="63"/>
       <c r="F16" s="43"/>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B17" s="43">
         <v>3</v>
       </c>
-      <c r="C17" s="63"/>
-      <c r="D17" s="65"/>
-      <c r="E17" s="65"/>
+      <c r="C17" s="61"/>
+      <c r="D17" s="63"/>
+      <c r="E17" s="63"/>
       <c r="F17" s="43"/>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B18" s="43">
         <v>4</v>
       </c>
-      <c r="C18" s="63"/>
-      <c r="D18" s="63"/>
-      <c r="E18" s="63"/>
+      <c r="C18" s="61"/>
+      <c r="D18" s="61"/>
+      <c r="E18" s="61"/>
       <c r="F18" s="43"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B19" s="43">
         <v>5</v>
       </c>
-      <c r="C19" s="63"/>
-      <c r="D19" s="63"/>
-      <c r="E19" s="63"/>
+      <c r="C19" s="61"/>
+      <c r="D19" s="61"/>
+      <c r="E19" s="61"/>
       <c r="F19" s="43"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B20" s="43">
         <v>6</v>
       </c>
-      <c r="C20" s="63"/>
-      <c r="D20" s="63"/>
-      <c r="E20" s="63"/>
+      <c r="C20" s="61"/>
+      <c r="D20" s="61"/>
+      <c r="E20" s="61"/>
       <c r="F20" s="43"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B21" s="43">
         <v>7</v>
       </c>
-      <c r="C21" s="63"/>
-      <c r="D21" s="63"/>
-      <c r="E21" s="63"/>
+      <c r="C21" s="61"/>
+      <c r="D21" s="61"/>
+      <c r="E21" s="61"/>
       <c r="F21" s="43"/>
     </row>
     <row r="22" spans="2:6" ht="30" x14ac:dyDescent="0.25">
       <c r="B22" s="43"/>
-      <c r="C22" s="64" t="s">
+      <c r="C22" s="62" t="s">
         <v>93</v>
       </c>
-      <c r="D22" s="64" t="s">
+      <c r="D22" s="62" t="s">
         <v>93</v>
       </c>
       <c r="E22" s="43"/>
@@ -1962,215 +2003,273 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:J26"/>
+  <dimension ref="B2:L26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.28515625" customWidth="1"/>
-    <col min="6" max="6" width="11.28515625" customWidth="1"/>
-    <col min="10" max="10" width="13.5703125" customWidth="1"/>
+    <col min="8" max="8" width="11.28515625" customWidth="1"/>
+    <col min="12" max="12" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2" s="43" t="s">
         <v>42</v>
       </c>
       <c r="C2" s="43"/>
-      <c r="D2" s="43" t="s">
+      <c r="D2" s="43"/>
+      <c r="E2" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="43"/>
       <c r="F2" s="43"/>
-      <c r="G2" s="43" t="s">
+      <c r="G2" s="43"/>
+      <c r="H2" s="43"/>
+      <c r="I2" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="43"/>
-      <c r="I2" s="43"/>
-      <c r="J2" s="43" t="s">
+      <c r="J2" s="43"/>
+      <c r="K2" s="43"/>
+      <c r="L2" s="43" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="43"/>
       <c r="C3" s="47" t="s">
         <v>97</v>
       </c>
       <c r="D3" s="47" t="s">
+        <v>99</v>
+      </c>
+      <c r="E3" s="47" t="s">
         <v>75</v>
       </c>
-      <c r="E3" s="47"/>
       <c r="F3" s="47" t="s">
+        <v>75</v>
+      </c>
+      <c r="G3" s="47"/>
+      <c r="H3" s="47" t="s">
         <v>65</v>
       </c>
-      <c r="G3" s="47" t="s">
+      <c r="I3" s="47" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="47" t="s">
+      <c r="J3" s="47" t="s">
         <v>66</v>
       </c>
-      <c r="I3" s="47"/>
-      <c r="J3" s="47" t="s">
+      <c r="K3" s="47"/>
+      <c r="L3" s="47" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="4" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="45" t="s">
         <v>67</v>
       </c>
       <c r="C4" s="48" t="s">
         <v>98</v>
       </c>
-      <c r="D4" s="61"/>
-      <c r="E4" s="49"/>
-      <c r="F4" s="68" t="s">
+      <c r="D4" s="48" t="s">
+        <v>101</v>
+      </c>
+      <c r="E4" s="59"/>
+      <c r="F4" s="49" t="s">
+        <v>104</v>
+      </c>
+      <c r="G4" s="49"/>
+      <c r="H4" s="66" t="s">
         <v>78</v>
       </c>
-      <c r="G4" s="61"/>
-      <c r="H4" s="49"/>
-      <c r="I4" s="49"/>
-      <c r="J4" s="50" t="s">
+      <c r="I4" s="59"/>
+      <c r="J4" s="49"/>
+      <c r="K4" s="49"/>
+      <c r="L4" s="50" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B5" s="46" t="s">
         <v>68</v>
       </c>
       <c r="C5" s="48" t="s">
         <v>98</v>
       </c>
-      <c r="D5" s="58"/>
-      <c r="E5" s="43"/>
-      <c r="F5" s="68" t="s">
+      <c r="D5" s="67"/>
+      <c r="E5" s="57"/>
+      <c r="F5" s="43"/>
+      <c r="G5" s="70"/>
+      <c r="H5" s="66" t="s">
         <v>78</v>
       </c>
-      <c r="G5" s="58"/>
-      <c r="H5" s="43"/>
-      <c r="I5" s="43"/>
-      <c r="J5" s="59"/>
-    </row>
-    <row r="6" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I5" s="57"/>
+      <c r="J5" s="43"/>
+      <c r="K5" s="43"/>
+      <c r="L5" s="52" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="46"/>
       <c r="C6" s="51"/>
-      <c r="D6" s="43"/>
+      <c r="D6" s="68"/>
       <c r="E6" s="43"/>
       <c r="F6" s="43"/>
       <c r="G6" s="43"/>
-      <c r="H6" s="43"/>
+      <c r="H6" s="43" t="s">
+        <v>100</v>
+      </c>
       <c r="I6" s="43"/>
-      <c r="J6" s="52"/>
-    </row>
-    <row r="7" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J6" s="43"/>
+      <c r="K6" s="43"/>
+      <c r="L6" s="52"/>
+    </row>
+    <row r="7" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="46" t="s">
         <v>69</v>
       </c>
       <c r="C7" s="48" t="s">
         <v>98</v>
       </c>
-      <c r="D7" s="58"/>
-      <c r="E7" s="43"/>
-      <c r="F7" s="67" t="s">
+      <c r="D7" s="48" t="s">
+        <v>101</v>
+      </c>
+      <c r="E7" s="57" t="s">
+        <v>103</v>
+      </c>
+      <c r="F7" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="G7" s="43"/>
+      <c r="H7" s="65" t="s">
         <v>80</v>
       </c>
-      <c r="G7" s="58"/>
-      <c r="H7" s="43"/>
-      <c r="I7" s="43"/>
-      <c r="J7" s="52" t="s">
+      <c r="I7" s="57"/>
+      <c r="J7" s="43"/>
+      <c r="K7" s="43"/>
+      <c r="L7" s="52" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B8" s="45" t="s">
         <v>70</v>
       </c>
       <c r="C8" s="48" t="s">
         <v>98</v>
       </c>
-      <c r="D8" s="58"/>
-      <c r="E8" s="44"/>
+      <c r="D8" s="67"/>
+      <c r="E8" s="57"/>
       <c r="F8" s="44"/>
-      <c r="G8" s="58"/>
-      <c r="H8" s="44"/>
-      <c r="I8" s="44"/>
-      <c r="J8" s="54"/>
-    </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="G8" s="44"/>
+      <c r="H8" s="44" t="s">
+        <v>100</v>
+      </c>
+      <c r="I8" s="57"/>
+      <c r="J8" s="44"/>
+      <c r="K8" s="44"/>
+      <c r="L8" s="52" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B9" s="46" t="s">
         <v>71</v>
       </c>
       <c r="C9" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="43"/>
+      <c r="D9" s="68"/>
       <c r="E9" s="43"/>
       <c r="F9" s="43"/>
-      <c r="G9" s="58"/>
-      <c r="H9" s="43"/>
-      <c r="I9" s="43"/>
-      <c r="J9" s="52"/>
-    </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="G9" s="43"/>
+      <c r="H9" s="43" t="s">
+        <v>100</v>
+      </c>
+      <c r="I9" s="57"/>
+      <c r="J9" s="43"/>
+      <c r="K9" s="43"/>
+      <c r="L9" s="52"/>
+    </row>
+    <row r="10" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="46"/>
       <c r="C10" s="51"/>
-      <c r="D10" s="43"/>
+      <c r="D10" s="68"/>
       <c r="E10" s="43"/>
       <c r="F10" s="43"/>
       <c r="G10" s="43"/>
       <c r="H10" s="43"/>
       <c r="I10" s="43"/>
-      <c r="J10" s="52"/>
-    </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J10" s="43"/>
+      <c r="K10" s="43"/>
+      <c r="L10" s="52"/>
+    </row>
+    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B11" s="45" t="s">
         <v>72</v>
       </c>
       <c r="C11" s="53" t="s">
         <v>19</v>
       </c>
-      <c r="D11" s="58"/>
-      <c r="E11" s="44"/>
-      <c r="F11" s="66" t="s">
+      <c r="D11" s="48" t="s">
+        <v>101</v>
+      </c>
+      <c r="E11" s="57" t="s">
+        <v>102</v>
+      </c>
+      <c r="F11" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="G11" s="44"/>
+      <c r="H11" s="64" t="s">
         <v>96</v>
       </c>
-      <c r="G11" s="58"/>
-      <c r="H11" s="44"/>
-      <c r="I11" s="44"/>
-      <c r="J11" s="52" t="s">
+      <c r="I11" s="57"/>
+      <c r="J11" s="44"/>
+      <c r="K11" s="44"/>
+      <c r="L11" s="52" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B12" s="46" t="s">
         <v>73</v>
       </c>
       <c r="C12" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="D12" s="58"/>
-      <c r="E12" s="43"/>
-      <c r="F12" s="66" t="s">
+      <c r="D12" s="68"/>
+      <c r="E12" s="57"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="43"/>
+      <c r="H12" s="64" t="s">
         <v>96</v>
       </c>
-      <c r="G12" s="58"/>
-      <c r="H12" s="43"/>
-      <c r="I12" s="43"/>
-      <c r="J12" s="52"/>
-    </row>
-    <row r="13" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I12" s="57"/>
+      <c r="J12" s="43"/>
+      <c r="K12" s="43"/>
+      <c r="L12" s="52" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B13" s="45" t="s">
         <v>74</v>
       </c>
-      <c r="C13" s="55" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" s="60"/>
-      <c r="E13" s="56"/>
-      <c r="F13" s="60"/>
-      <c r="G13" s="60"/>
-      <c r="H13" s="56"/>
-      <c r="I13" s="56"/>
-      <c r="J13" s="57"/>
-    </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="C13" s="54" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="69"/>
+      <c r="E13" s="58"/>
+      <c r="F13" s="55"/>
+      <c r="G13" s="55"/>
+      <c r="H13" s="58" t="s">
+        <v>100</v>
+      </c>
+      <c r="I13" s="58"/>
+      <c r="J13" s="55"/>
+      <c r="K13" s="55"/>
+      <c r="L13" s="56"/>
+    </row>
+    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>82</v>
       </c>
@@ -2191,7 +2290,7 @@
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B21" s="62"/>
+      <c r="B21" s="60"/>
       <c r="C21" t="s">
         <v>86</v>
       </c>

--- a/reestr.xlsx
+++ b/reestr.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16665" windowHeight="8130" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16665" windowHeight="8130" firstSheet="2" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Школа № 1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="107">
   <si>
     <t>Спортзал</t>
   </si>
@@ -344,6 +344,9 @@
   </si>
   <si>
     <t>4.СКБ-Пт</t>
+  </si>
+  <si>
+    <t>Покраска</t>
   </si>
 </sst>
 </file>
@@ -408,7 +411,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="28">
+  <borders count="29">
     <border>
       <left/>
       <right/>
@@ -771,11 +774,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -955,6 +969,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1846,8 +1863,8 @@
         <v>1</v>
       </c>
       <c r="C6" s="61"/>
-      <c r="D6" s="63"/>
-      <c r="E6" s="63"/>
+      <c r="D6" s="61"/>
+      <c r="E6" s="61"/>
       <c r="F6" s="43"/>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.25">
@@ -1855,8 +1872,8 @@
         <v>2</v>
       </c>
       <c r="C7" s="61"/>
-      <c r="D7" s="63"/>
-      <c r="E7" s="63"/>
+      <c r="D7" s="61"/>
+      <c r="E7" s="61"/>
       <c r="F7" s="43"/>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.25">
@@ -1927,7 +1944,7 @@
         <v>1</v>
       </c>
       <c r="C15" s="61"/>
-      <c r="D15" s="63"/>
+      <c r="D15" s="61"/>
       <c r="E15" s="63"/>
       <c r="F15" s="43"/>
     </row>
@@ -1936,8 +1953,8 @@
         <v>2</v>
       </c>
       <c r="C16" s="61"/>
-      <c r="D16" s="63"/>
-      <c r="E16" s="63"/>
+      <c r="D16" s="61"/>
+      <c r="E16" s="61"/>
       <c r="F16" s="43"/>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.25">
@@ -2003,15 +2020,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:L26"/>
+  <dimension ref="B2:M26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.28515625" customWidth="1"/>
     <col min="8" max="8" width="11.28515625" customWidth="1"/>
-    <col min="12" max="12" width="13.5703125" customWidth="1"/>
+    <col min="12" max="13" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B2" s="43" t="s">
         <v>42</v>
       </c>
@@ -2031,8 +2048,9 @@
       <c r="L2" s="43" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M2" s="81"/>
+    </row>
+    <row r="3" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="43"/>
       <c r="C3" s="47" t="s">
         <v>97</v>
@@ -2060,8 +2078,11 @@
       <c r="L3" s="47" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="4" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M3" s="83" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="4" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="45" t="s">
         <v>67</v>
       </c>
@@ -2085,8 +2106,9 @@
       <c r="L4" s="50" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M4" s="82"/>
+    </row>
+    <row r="5" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B5" s="46" t="s">
         <v>68</v>
       </c>
@@ -2106,8 +2128,9 @@
       <c r="L5" s="52" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="6" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M5" s="81"/>
+    </row>
+    <row r="6" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="46"/>
       <c r="C6" s="51"/>
       <c r="D6" s="68"/>
@@ -2121,8 +2144,9 @@
       <c r="J6" s="43"/>
       <c r="K6" s="43"/>
       <c r="L6" s="52"/>
-    </row>
-    <row r="7" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M6" s="81"/>
+    </row>
+    <row r="7" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="46" t="s">
         <v>69</v>
       </c>
@@ -2148,8 +2172,9 @@
       <c r="L7" s="52" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M7" s="81"/>
+    </row>
+    <row r="8" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B8" s="45" t="s">
         <v>70</v>
       </c>
@@ -2169,8 +2194,9 @@
       <c r="L8" s="52" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M8" s="81"/>
+    </row>
+    <row r="9" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B9" s="46" t="s">
         <v>71</v>
       </c>
@@ -2188,8 +2214,9 @@
       <c r="J9" s="43"/>
       <c r="K9" s="43"/>
       <c r="L9" s="52"/>
-    </row>
-    <row r="10" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M9" s="81"/>
+    </row>
+    <row r="10" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="46"/>
       <c r="C10" s="51"/>
       <c r="D10" s="68"/>
@@ -2201,8 +2228,9 @@
       <c r="J10" s="43"/>
       <c r="K10" s="43"/>
       <c r="L10" s="52"/>
-    </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M10" s="81"/>
+    </row>
+    <row r="11" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B11" s="45" t="s">
         <v>72</v>
       </c>
@@ -2228,8 +2256,9 @@
       <c r="L11" s="52" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M11" s="81"/>
+    </row>
+    <row r="12" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B12" s="46" t="s">
         <v>73</v>
       </c>
@@ -2249,8 +2278,9 @@
       <c r="L12" s="52" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="13" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M12" s="81"/>
+    </row>
+    <row r="13" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B13" s="45" t="s">
         <v>74</v>
       </c>
@@ -2268,8 +2298,9 @@
       <c r="J13" s="55"/>
       <c r="K13" s="55"/>
       <c r="L13" s="56"/>
-    </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M13" s="82"/>
+    </row>
+    <row r="16" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>82</v>
       </c>
